--- a/output/yearly_total_coral_cover_iteration_95_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_95_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.269739893568693</v>
+        <v>1.26761931852752</v>
       </c>
       <c r="C3" t="n">
-        <v>4.590835742938942</v>
+        <v>4.614446775226077</v>
       </c>
       <c r="D3" t="n">
-        <v>6.081666958602004</v>
+        <v>6.08928532078696</v>
       </c>
       <c r="E3" t="n">
-        <v>11.94224259510964</v>
+        <v>11.97135141454056</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.416934607076757</v>
+        <v>1.412531375356435</v>
       </c>
       <c r="C4" t="n">
-        <v>5.012255084359916</v>
+        <v>5.115390946153267</v>
       </c>
       <c r="D4" t="n">
-        <v>6.37652615278882</v>
+        <v>6.318033036098583</v>
       </c>
       <c r="E4" t="n">
-        <v>12.80571584422549</v>
+        <v>12.84595535760828</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.617487723647913</v>
+        <v>1.603710217850179</v>
       </c>
       <c r="C5" t="n">
-        <v>5.519145500547963</v>
+        <v>5.778968795749829</v>
       </c>
       <c r="D5" t="n">
-        <v>6.719332298286159</v>
+        <v>6.612829485648582</v>
       </c>
       <c r="E5" t="n">
-        <v>13.85596552248203</v>
+        <v>13.99550849924859</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.843873349829561</v>
+        <v>1.819533086578561</v>
       </c>
       <c r="C6" t="n">
-        <v>6.117490079203051</v>
+        <v>6.582012831165141</v>
       </c>
       <c r="D6" t="n">
-        <v>7.02686036287607</v>
+        <v>6.908095558299109</v>
       </c>
       <c r="E6" t="n">
-        <v>14.98822379190868</v>
+        <v>15.30964147604281</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.101607249974642</v>
+        <v>2.059026325769514</v>
       </c>
       <c r="C7" t="n">
-        <v>6.821693586683558</v>
+        <v>7.539258475249203</v>
       </c>
       <c r="D7" t="n">
-        <v>7.487039242429826</v>
+        <v>7.184108338422491</v>
       </c>
       <c r="E7" t="n">
-        <v>16.41034007908803</v>
+        <v>16.78239313944121</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.334408659339344</v>
+        <v>1.265173422969165</v>
       </c>
       <c r="C8" t="n">
-        <v>4.461804006650265</v>
+        <v>5.189027488874404</v>
       </c>
       <c r="D8" t="n">
-        <v>5.731956673517355</v>
+        <v>5.33874283744314</v>
       </c>
       <c r="E8" t="n">
-        <v>11.52816933950696</v>
+        <v>11.79294374928671</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.731987212474345</v>
+        <v>1.586758087132579</v>
       </c>
       <c r="C9" t="n">
-        <v>5.389300767117697</v>
+        <v>6.341634490318397</v>
       </c>
       <c r="D9" t="n">
-        <v>6.310224334362703</v>
+        <v>5.804008930970213</v>
       </c>
       <c r="E9" t="n">
-        <v>13.43151231395474</v>
+        <v>13.73240150842119</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.161586398445255</v>
+        <v>1.940606543553394</v>
       </c>
       <c r="C10" t="n">
-        <v>6.469038218853639</v>
+        <v>7.615771477856472</v>
       </c>
       <c r="D10" t="n">
-        <v>6.963874016107826</v>
+        <v>6.274512148996854</v>
       </c>
       <c r="E10" t="n">
-        <v>15.59449863340672</v>
+        <v>15.83089017040672</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.604482171215957</v>
+        <v>2.320078965804025</v>
       </c>
       <c r="C11" t="n">
-        <v>7.639412759832535</v>
+        <v>8.97160037780465</v>
       </c>
       <c r="D11" t="n">
-        <v>7.62376962632954</v>
+        <v>6.72582433121211</v>
       </c>
       <c r="E11" t="n">
-        <v>17.86766455737803</v>
+        <v>18.01750367482078</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.048876248854055</v>
+        <v>2.703590350679133</v>
       </c>
       <c r="C12" t="n">
-        <v>8.883106455491536</v>
+        <v>10.43938284245554</v>
       </c>
       <c r="D12" t="n">
-        <v>8.305015974826214</v>
+        <v>7.168597199013215</v>
       </c>
       <c r="E12" t="n">
-        <v>20.2369986791718</v>
+        <v>20.31157039214789</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.484709788969224</v>
+        <v>3.088315960186275</v>
       </c>
       <c r="C13" t="n">
-        <v>10.14787755568922</v>
+        <v>11.95571880962573</v>
       </c>
       <c r="D13" t="n">
-        <v>8.962142692937135</v>
+        <v>7.568985290061953</v>
       </c>
       <c r="E13" t="n">
-        <v>22.59473003759557</v>
+        <v>22.61302005987396</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.989757159582223</v>
+        <v>1.780664533531737</v>
       </c>
       <c r="C14" t="n">
-        <v>7.13391878029466</v>
+        <v>8.472158710907573</v>
       </c>
       <c r="D14" t="n">
-        <v>6.856633958707191</v>
+        <v>5.773402994272387</v>
       </c>
       <c r="E14" t="n">
-        <v>15.98030989858407</v>
+        <v>16.0262262387117</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.074000930083642</v>
+        <v>1.852440108189222</v>
       </c>
       <c r="C15" t="n">
-        <v>7.578297061144936</v>
+        <v>9.087734156424407</v>
       </c>
       <c r="D15" t="n">
-        <v>6.992213316663674</v>
+        <v>5.7413882016369</v>
       </c>
       <c r="E15" t="n">
-        <v>16.64451130789225</v>
+        <v>16.68156246625053</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.453328608050525</v>
+        <v>2.183524703969416</v>
       </c>
       <c r="C16" t="n">
-        <v>8.850259204244146</v>
+        <v>10.69874286918525</v>
       </c>
       <c r="D16" t="n">
-        <v>7.652320838045146</v>
+        <v>6.162508879373569</v>
       </c>
       <c r="E16" t="n">
-        <v>18.95590865033982</v>
+        <v>19.04477645252824</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.005268773309323</v>
+        <v>1.777856735097592</v>
       </c>
       <c r="C17" t="n">
-        <v>8.124129149752077</v>
+        <v>9.822395598466381</v>
       </c>
       <c r="D17" t="n">
-        <v>7.239976984784442</v>
+        <v>5.697533531688195</v>
       </c>
       <c r="E17" t="n">
-        <v>17.36937490784584</v>
+        <v>17.29778586525217</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.331778424787727</v>
+        <v>2.054434698338003</v>
       </c>
       <c r="C18" t="n">
-        <v>9.366992290897413</v>
+        <v>11.47095616091467</v>
       </c>
       <c r="D18" t="n">
-        <v>7.807093363619655</v>
+        <v>6.086600146881206</v>
       </c>
       <c r="E18" t="n">
-        <v>19.5058640793048</v>
+        <v>19.61199100613388</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.378116916428176</v>
+        <v>2.080343020253077</v>
       </c>
       <c r="C19" t="n">
-        <v>9.905579081447213</v>
+        <v>12.27389815578701</v>
       </c>
       <c r="D19" t="n">
-        <v>8.006378330104715</v>
+        <v>6.161487861761152</v>
       </c>
       <c r="E19" t="n">
-        <v>20.2900743279801</v>
+        <v>20.51572903780124</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.681938378461437</v>
+        <v>2.341301377518921</v>
       </c>
       <c r="C20" t="n">
-        <v>11.33994192978293</v>
+        <v>14.16663900723556</v>
       </c>
       <c r="D20" t="n">
-        <v>8.603457648873542</v>
+        <v>6.568903341546536</v>
       </c>
       <c r="E20" t="n">
-        <v>22.62533795711791</v>
+        <v>23.07684372630101</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.612334072161579</v>
+        <v>1.406157236792707</v>
       </c>
       <c r="C21" t="n">
-        <v>8.328205045033862</v>
+        <v>10.51509714362884</v>
       </c>
       <c r="D21" t="n">
-        <v>7.255743852914647</v>
+        <v>5.456082501305733</v>
       </c>
       <c r="E21" t="n">
-        <v>17.19628297011009</v>
+        <v>17.37733688172728</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_95_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_95_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.26761931852752</v>
+        <v>1.245755797153944</v>
       </c>
       <c r="C3" t="n">
-        <v>4.614446775226077</v>
+        <v>4.598316660445302</v>
       </c>
       <c r="D3" t="n">
-        <v>6.08928532078696</v>
+        <v>6.042033803781561</v>
       </c>
       <c r="E3" t="n">
-        <v>11.97135141454056</v>
+        <v>11.88610626138081</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.412531375356435</v>
+        <v>1.355477047401666</v>
       </c>
       <c r="C4" t="n">
-        <v>5.115390946153267</v>
+        <v>5.066890851058057</v>
       </c>
       <c r="D4" t="n">
-        <v>6.318033036098583</v>
+        <v>6.261319196646962</v>
       </c>
       <c r="E4" t="n">
-        <v>12.84595535760828</v>
+        <v>12.68368709510668</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.603710217850179</v>
+        <v>1.502736196859642</v>
       </c>
       <c r="C5" t="n">
-        <v>5.778968795749829</v>
+        <v>5.67341298356721</v>
       </c>
       <c r="D5" t="n">
-        <v>6.612829485648582</v>
+        <v>6.507812183148566</v>
       </c>
       <c r="E5" t="n">
-        <v>13.99550849924859</v>
+        <v>13.68396136357542</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.819533086578561</v>
+        <v>1.684449881451555</v>
       </c>
       <c r="C6" t="n">
-        <v>6.582012831165141</v>
+        <v>6.439800589806389</v>
       </c>
       <c r="D6" t="n">
-        <v>6.908095558299109</v>
+        <v>6.849263947319916</v>
       </c>
       <c r="E6" t="n">
-        <v>15.30964147604281</v>
+        <v>14.97351441857786</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.059026325769514</v>
+        <v>1.895126991411381</v>
       </c>
       <c r="C7" t="n">
-        <v>7.539258475249203</v>
+        <v>7.335862357079137</v>
       </c>
       <c r="D7" t="n">
-        <v>7.184108338422491</v>
+        <v>7.166332537322972</v>
       </c>
       <c r="E7" t="n">
-        <v>16.78239313944121</v>
+        <v>16.39732188581349</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.265173422969165</v>
+        <v>1.159581433173437</v>
       </c>
       <c r="C8" t="n">
-        <v>5.189027488874404</v>
+        <v>5.036674496216889</v>
       </c>
       <c r="D8" t="n">
-        <v>5.33874283744314</v>
+        <v>5.364964004839846</v>
       </c>
       <c r="E8" t="n">
-        <v>11.79294374928671</v>
+        <v>11.56121993423017</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.586758087132579</v>
+        <v>1.461574706703495</v>
       </c>
       <c r="C9" t="n">
-        <v>6.341634490318397</v>
+        <v>6.240956725938361</v>
       </c>
       <c r="D9" t="n">
-        <v>5.804008930970213</v>
+        <v>5.774962058627438</v>
       </c>
       <c r="E9" t="n">
-        <v>13.73240150842119</v>
+        <v>13.47749349126929</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.940606543553394</v>
+        <v>1.772251351471518</v>
       </c>
       <c r="C10" t="n">
-        <v>7.615771477856472</v>
+        <v>7.686708697787296</v>
       </c>
       <c r="D10" t="n">
-        <v>6.274512148996854</v>
+        <v>6.243964882160101</v>
       </c>
       <c r="E10" t="n">
-        <v>15.83089017040672</v>
+        <v>15.70292493141891</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.320078965804025</v>
+        <v>2.087481872595343</v>
       </c>
       <c r="C11" t="n">
-        <v>8.97160037780465</v>
+        <v>9.297017919978042</v>
       </c>
       <c r="D11" t="n">
-        <v>6.72582433121211</v>
+        <v>6.693013944612468</v>
       </c>
       <c r="E11" t="n">
-        <v>18.01750367482078</v>
+        <v>18.07751373718585</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.703590350679133</v>
+        <v>2.39406141464608</v>
       </c>
       <c r="C12" t="n">
-        <v>10.43938284245554</v>
+        <v>11.03147922845656</v>
       </c>
       <c r="D12" t="n">
-        <v>7.168597199013215</v>
+        <v>7.109602034036636</v>
       </c>
       <c r="E12" t="n">
-        <v>20.31157039214789</v>
+        <v>20.53514267713928</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.088315960186275</v>
+        <v>2.692898869217652</v>
       </c>
       <c r="C13" t="n">
-        <v>11.95571880962573</v>
+        <v>12.80413295545326</v>
       </c>
       <c r="D13" t="n">
-        <v>7.568985290061953</v>
+        <v>7.497188367718932</v>
       </c>
       <c r="E13" t="n">
-        <v>22.61302005987396</v>
+        <v>22.99422019238985</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.780664533531737</v>
+        <v>1.557788169713627</v>
       </c>
       <c r="C14" t="n">
-        <v>8.472158710907573</v>
+        <v>8.918637931844936</v>
       </c>
       <c r="D14" t="n">
-        <v>5.773402994272387</v>
+        <v>5.717021223617493</v>
       </c>
       <c r="E14" t="n">
-        <v>16.0262262387117</v>
+        <v>16.19344732517606</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.852440108189222</v>
+        <v>1.585905423963255</v>
       </c>
       <c r="C15" t="n">
-        <v>9.087734156424407</v>
+        <v>9.770235342939747</v>
       </c>
       <c r="D15" t="n">
-        <v>5.7413882016369</v>
+        <v>5.675630740406448</v>
       </c>
       <c r="E15" t="n">
-        <v>16.68156246625053</v>
+        <v>17.03177150730945</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.183524703969416</v>
+        <v>1.829467211909846</v>
       </c>
       <c r="C16" t="n">
-        <v>10.69874286918525</v>
+        <v>11.61502763651289</v>
       </c>
       <c r="D16" t="n">
-        <v>6.162508879373569</v>
+        <v>6.086786678945012</v>
       </c>
       <c r="E16" t="n">
-        <v>19.04477645252824</v>
+        <v>19.53128152736775</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.777856735097592</v>
+        <v>1.456265639617464</v>
       </c>
       <c r="C17" t="n">
-        <v>9.822395598466381</v>
+        <v>10.76472613238768</v>
       </c>
       <c r="D17" t="n">
-        <v>5.697533531688195</v>
+        <v>5.591013905777415</v>
       </c>
       <c r="E17" t="n">
-        <v>17.29778586525217</v>
+        <v>17.81200567778256</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.054434698338003</v>
+        <v>1.660567336871225</v>
       </c>
       <c r="C18" t="n">
-        <v>11.47095616091467</v>
+        <v>12.61616485791857</v>
       </c>
       <c r="D18" t="n">
-        <v>6.086600146881206</v>
+        <v>5.961820013671436</v>
       </c>
       <c r="E18" t="n">
-        <v>19.61199100613388</v>
+        <v>20.23855220846123</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.080343020253077</v>
+        <v>1.665446622961332</v>
       </c>
       <c r="C19" t="n">
-        <v>12.27389815578701</v>
+        <v>13.54074539334709</v>
       </c>
       <c r="D19" t="n">
-        <v>6.161487861761152</v>
+        <v>6.030414725767161</v>
       </c>
       <c r="E19" t="n">
-        <v>20.51572903780124</v>
+        <v>21.23660674207558</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.341301377518921</v>
+        <v>1.85306842671994</v>
       </c>
       <c r="C20" t="n">
-        <v>14.16663900723556</v>
+        <v>15.57577093957213</v>
       </c>
       <c r="D20" t="n">
-        <v>6.568903341546536</v>
+        <v>6.392581453863809</v>
       </c>
       <c r="E20" t="n">
-        <v>23.07684372630101</v>
+        <v>23.82142082015588</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.406157236792707</v>
+        <v>1.105948606311075</v>
       </c>
       <c r="C21" t="n">
-        <v>10.51509714362884</v>
+        <v>11.40707383779933</v>
       </c>
       <c r="D21" t="n">
-        <v>5.456082501305733</v>
+        <v>5.308309836862504</v>
       </c>
       <c r="E21" t="n">
-        <v>17.37733688172728</v>
+        <v>17.82133228097291</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_95_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_95_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.245755797153944</v>
+        <v>2.573847478107392</v>
       </c>
       <c r="C3" t="n">
-        <v>4.598316660445302</v>
+        <v>7.815975349699595</v>
       </c>
       <c r="D3" t="n">
-        <v>6.042033803781561</v>
+        <v>8.234249594794864</v>
       </c>
       <c r="E3" t="n">
-        <v>11.88610626138081</v>
+        <v>18.62407242260185</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.355477047401666</v>
+        <v>1.038518381295272</v>
       </c>
       <c r="C4" t="n">
-        <v>5.066890851058057</v>
+        <v>4.737785650318293</v>
       </c>
       <c r="D4" t="n">
-        <v>6.261319196646962</v>
+        <v>5.806015745663121</v>
       </c>
       <c r="E4" t="n">
-        <v>12.68368709510668</v>
+        <v>11.58231977727669</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.502736196859642</v>
+        <v>1.115186447474143</v>
       </c>
       <c r="C5" t="n">
-        <v>5.67341298356721</v>
+        <v>5.603431401410184</v>
       </c>
       <c r="D5" t="n">
-        <v>6.507812183148566</v>
+        <v>6.0744812901045</v>
       </c>
       <c r="E5" t="n">
-        <v>13.68396136357542</v>
+        <v>12.79309913898883</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.684449881451555</v>
+        <v>1.20216202477137</v>
       </c>
       <c r="C6" t="n">
-        <v>6.439800589806389</v>
+        <v>6.666117713417425</v>
       </c>
       <c r="D6" t="n">
-        <v>6.849263947319916</v>
+        <v>6.41868811880659</v>
       </c>
       <c r="E6" t="n">
-        <v>14.97351441857786</v>
+        <v>14.28696785699538</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.895126991411381</v>
+        <v>1.291852308850564</v>
       </c>
       <c r="C7" t="n">
-        <v>7.335862357079137</v>
+        <v>7.8383100894015</v>
       </c>
       <c r="D7" t="n">
-        <v>7.166332537322972</v>
+        <v>6.759163970795098</v>
       </c>
       <c r="E7" t="n">
-        <v>16.39732188581349</v>
+        <v>15.88932636904716</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.159581433173437</v>
+        <v>1.383413001695895</v>
       </c>
       <c r="C8" t="n">
-        <v>5.036674496216889</v>
+        <v>9.13477481525689</v>
       </c>
       <c r="D8" t="n">
-        <v>5.364964004839846</v>
+        <v>7.23334108510638</v>
       </c>
       <c r="E8" t="n">
-        <v>11.56121993423017</v>
+        <v>17.75152890205916</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.461574706703495</v>
+        <v>1.453680595662332</v>
       </c>
       <c r="C9" t="n">
-        <v>6.240956725938361</v>
+        <v>10.55752956090276</v>
       </c>
       <c r="D9" t="n">
-        <v>5.774962058627438</v>
+        <v>7.6501571336048</v>
       </c>
       <c r="E9" t="n">
-        <v>13.47749349126929</v>
+        <v>19.66136729016989</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.772251351471518</v>
+        <v>0.9222930632776235</v>
       </c>
       <c r="C10" t="n">
-        <v>7.686708697787296</v>
+        <v>7.603321810126189</v>
       </c>
       <c r="D10" t="n">
-        <v>6.243964882160101</v>
+        <v>6.020096557395526</v>
       </c>
       <c r="E10" t="n">
-        <v>15.70292493141891</v>
+        <v>14.54571143079934</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.087481872595343</v>
+        <v>0.8318937346705773</v>
       </c>
       <c r="C11" t="n">
-        <v>9.297017919978042</v>
+        <v>8.13751037096096</v>
       </c>
       <c r="D11" t="n">
-        <v>6.693013944612468</v>
+        <v>5.887668609569674</v>
       </c>
       <c r="E11" t="n">
-        <v>18.07751373718585</v>
+        <v>14.85707271520121</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.39406141464608</v>
+        <v>0.8654989585869456</v>
       </c>
       <c r="C12" t="n">
-        <v>11.03147922845656</v>
+        <v>9.622531400835815</v>
       </c>
       <c r="D12" t="n">
-        <v>7.109602034036636</v>
+        <v>6.338418433020512</v>
       </c>
       <c r="E12" t="n">
-        <v>20.53514267713928</v>
+        <v>16.82644879244327</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.692898869217652</v>
+        <v>0.668236392372634</v>
       </c>
       <c r="C13" t="n">
-        <v>12.80413295545326</v>
+        <v>9.11574341842657</v>
       </c>
       <c r="D13" t="n">
-        <v>7.497188367718932</v>
+        <v>5.809511674834585</v>
       </c>
       <c r="E13" t="n">
-        <v>22.99422019238985</v>
+        <v>15.59349148563379</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.557788169713627</v>
+        <v>0.7035400398173494</v>
       </c>
       <c r="C14" t="n">
-        <v>8.918637931844936</v>
+        <v>10.64841848186556</v>
       </c>
       <c r="D14" t="n">
-        <v>5.717021223617493</v>
+        <v>6.211714074310419</v>
       </c>
       <c r="E14" t="n">
-        <v>16.19344732517606</v>
+        <v>17.56367259599333</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.585905423963255</v>
+        <v>0.6672546446683871</v>
       </c>
       <c r="C15" t="n">
-        <v>9.770235342939747</v>
+        <v>11.45868431461158</v>
       </c>
       <c r="D15" t="n">
-        <v>5.675630740406448</v>
+        <v>6.284873913230891</v>
       </c>
       <c r="E15" t="n">
-        <v>17.03177150730945</v>
+        <v>18.41081287251086</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.829467211909846</v>
+        <v>0.7215158402821084</v>
       </c>
       <c r="C16" t="n">
-        <v>11.61502763651289</v>
+        <v>13.2698124794061</v>
       </c>
       <c r="D16" t="n">
-        <v>6.086786678945012</v>
+        <v>6.754973983932434</v>
       </c>
       <c r="E16" t="n">
-        <v>19.53128152736775</v>
+        <v>20.74630230362064</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.456265639617464</v>
+        <v>0.4353363844941631</v>
       </c>
       <c r="C17" t="n">
-        <v>10.76472613238768</v>
+        <v>9.837219988800507</v>
       </c>
       <c r="D17" t="n">
-        <v>5.591013905777415</v>
+        <v>5.644882402309438</v>
       </c>
       <c r="E17" t="n">
-        <v>17.81200567778256</v>
+        <v>15.91743877560411</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.660567336871225</v>
+        <v>0.3354926429722625</v>
       </c>
       <c r="C18" t="n">
-        <v>12.61616485791857</v>
+        <v>8.648971472442424</v>
       </c>
       <c r="D18" t="n">
-        <v>5.961820013671436</v>
+        <v>5.203488634480072</v>
       </c>
       <c r="E18" t="n">
-        <v>20.23855220846123</v>
+        <v>14.18795274989476</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.665446622961332</v>
+        <v>0.3917369689485623</v>
       </c>
       <c r="C19" t="n">
-        <v>13.54074539334709</v>
+        <v>10.57662327225399</v>
       </c>
       <c r="D19" t="n">
-        <v>6.030414725767161</v>
+        <v>5.731727804227111</v>
       </c>
       <c r="E19" t="n">
-        <v>21.23660674207558</v>
+        <v>16.70008804542967</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.85306842671994</v>
+        <v>0.4435830652098364</v>
       </c>
       <c r="C20" t="n">
-        <v>15.57577093957213</v>
+        <v>12.60941043371335</v>
       </c>
       <c r="D20" t="n">
-        <v>6.392581453863809</v>
+        <v>6.25085635527874</v>
       </c>
       <c r="E20" t="n">
-        <v>23.82142082015588</v>
+        <v>19.30384985420193</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.105948606311075</v>
+        <v>0.4902455335926873</v>
       </c>
       <c r="C21" t="n">
-        <v>11.40707383779933</v>
+        <v>14.6440432808567</v>
       </c>
       <c r="D21" t="n">
-        <v>5.308309836862504</v>
+        <v>6.746030262346745</v>
       </c>
       <c r="E21" t="n">
-        <v>17.82133228097291</v>
+        <v>21.88031907679613</v>
       </c>
     </row>
   </sheetData>
